--- a/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC4/GradeDetail.xlsx
+++ b/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC4/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>47</x:v>
@@ -1360,7 +1360,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>47</x:v>
@@ -1413,7 +1413,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>64</x:v>
@@ -1528,7 +1528,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>47</x:v>
@@ -1581,7 +1581,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1637,7 +1637,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1693,7 +1693,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1752,7 +1752,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R14" s="4" t="s">
         <x:v>66</x:v>
@@ -1805,7 +1805,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1864,7 +1864,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R16" s="4" t="s">
         <x:v>66</x:v>
@@ -1920,7 +1920,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R17" s="4" t="s">
         <x:v>66</x:v>
@@ -1973,7 +1973,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q18" s="0">
         <x:v>4000</x:v>
@@ -2032,7 +2032,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R19" s="4" t="s">
         <x:v>66</x:v>
@@ -2085,7 +2085,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q20" s="0">
         <x:v>4000</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R21" s="4" t="s">
         <x:v>66</x:v>
@@ -2197,7 +2197,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2256,7 +2256,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R23" s="4" t="s">
         <x:v>66</x:v>
@@ -2309,7 +2309,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>4000</x:v>
@@ -2365,7 +2365,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P25" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q25" s="0">
         <x:v>4000</x:v>
@@ -2424,7 +2424,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q26" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R26" s="4" t="s">
         <x:v>66</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q27" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R27" s="4" t="s">
         <x:v>66</x:v>
@@ -2533,7 +2533,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P28" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q28" s="0">
         <x:v>4000</x:v>
@@ -2592,7 +2592,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q29" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R29" s="4" t="s">
         <x:v>66</x:v>
@@ -2645,7 +2645,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P30" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q30" s="0">
         <x:v>4000</x:v>
@@ -2704,7 +2704,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q31" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R31" s="4" t="s">
         <x:v>66</x:v>
@@ -2757,7 +2757,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P32" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q32" s="0">
         <x:v>4000</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q33" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R33" s="4" t="s">
         <x:v>66</x:v>
@@ -2869,7 +2869,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P34" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q34" s="0">
         <x:v>4000</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P35" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q35" s="0">
         <x:v>4000</x:v>
@@ -2984,7 +2984,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q36" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R36" s="4" t="s">
         <x:v>66</x:v>
@@ -3040,7 +3040,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q37" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R37" s="4" t="s">
         <x:v>66</x:v>
@@ -3093,7 +3093,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P38" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q38" s="0">
         <x:v>4000</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q39" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R39" s="4" t="s">
         <x:v>66</x:v>
@@ -3205,7 +3205,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P40" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q40" s="0">
         <x:v>4000</x:v>
@@ -3264,7 +3264,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q41" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R41" s="4" t="s">
         <x:v>66</x:v>
